--- a/data_input/crop_parameters_maiz_sugar.xlsx
+++ b/data_input/crop_parameters_maiz_sugar.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pyaez_github_test_env\input\maize_sugarcane_reduction_tables\M2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dario_outputs\maize_sugarcane_reduction_tables\M2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A6682A-4A61-45BE-BB63-33F28AA1989F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA136492-A361-4F8A-9B96-0EB5DC67D5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1980" yWindow="1350" windowWidth="26760" windowHeight="14145" xr2:uid="{0EBC9278-16C4-4F19-BFBC-BE9217943952}"/>
+    <workbookView xWindow="52695" yWindow="15" windowWidth="14610" windowHeight="15585" xr2:uid="{0EBC9278-16C4-4F19-BFBC-BE9217943952}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="48">
   <si>
     <t>Crop_name</t>
   </si>
@@ -177,6 +177,9 @@
   </si>
   <si>
     <t>HB_flag</t>
+  </si>
+  <si>
+    <t>winter_wheat</t>
   </si>
 </sst>
 </file>
@@ -536,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29C5A6A-0B2F-4690-8ED4-94CA56D6CD01}">
-  <dimension ref="A1:AM6"/>
+  <dimension ref="A1:AM7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
@@ -1272,6 +1275,125 @@
         <v>10950</v>
       </c>
     </row>
+    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7">
+        <v>0.45</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>209</v>
+      </c>
+      <c r="I7">
+        <v>167</v>
+      </c>
+      <c r="J7">
+        <v>230</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>0.3</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>23</v>
+      </c>
+      <c r="O7">
+        <v>36</v>
+      </c>
+      <c r="P7">
+        <v>31</v>
+      </c>
+      <c r="Q7">
+        <v>10</v>
+      </c>
+      <c r="R7">
+        <v>0.7</v>
+      </c>
+      <c r="S7">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="T7">
+        <v>0.4</v>
+      </c>
+      <c r="U7">
+        <v>0.85</v>
+      </c>
+      <c r="V7">
+        <v>0.2</v>
+      </c>
+      <c r="W7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="X7">
+        <v>0.3</v>
+      </c>
+      <c r="Y7">
+        <v>0.15</v>
+      </c>
+      <c r="Z7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH7">
+        <v>1520</v>
+      </c>
+      <c r="AI7">
+        <v>1600</v>
+      </c>
+      <c r="AJ7">
+        <v>1700</v>
+      </c>
+      <c r="AK7">
+        <v>2500</v>
+      </c>
+      <c r="AL7">
+        <v>2900</v>
+      </c>
+      <c r="AM7">
+        <v>3045</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1279,6 +1401,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008864D41C708CC54AABC64DB9F8EC5160" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8280e7c680d5d724f4413038ca100d1d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aecedfd1-a701-4d39-be9b-da32a8dfc2a5" xmlns:ns3="6cc8ca2e-56d8-406d-8e41-68c6b727753a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a78283ead66d0e44d8e1b525c3947135" ns2:_="" ns3:_="">
     <xsd:import namespace="aecedfd1-a701-4d39-be9b-da32a8dfc2a5"/>
@@ -1521,16 +1652,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A77A2D2-FB5E-4D16-89FD-0C1B6E08F2B9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3494866B-24BB-495E-916D-2E3A591177B2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1547,12 +1677,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A77A2D2-FB5E-4D16-89FD-0C1B6E08F2B9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>